--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE251EA-915E-8A47-A230-F51789F3A8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9622901A-0B48-4441-A19A-946C2D4C078E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5860" windowWidth="28040" windowHeight="10920" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="5860" windowWidth="28040" windowHeight="10920" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Infrastructure" sheetId="1" r:id="rId1"/>
@@ -637,7 +637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -718,6 +718,146 @@
       </c>
       <c r="F4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>40</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9622901A-0B48-4441-A19A-946C2D4C078E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9598BE4-F340-314D-8057-A9229BB6A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5860" windowWidth="28040" windowHeight="10920" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="5860" windowWidth="28040" windowHeight="10920" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Infrastructure" sheetId="1" r:id="rId1"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId2"/>
     <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
   <si>
     <t>type</t>
   </si>
@@ -867,7 +868,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -930,165 +931,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>70</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>110</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>45</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>60</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="K3" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>50</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9598BE4-F340-314D-8057-A9229BB6A086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95AA517-A307-2B4E-89E5-0D548B37372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5860" windowWidth="28040" windowHeight="10920" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="5860" windowWidth="28040" windowHeight="10920" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Infrastructure" sheetId="1" r:id="rId1"/>
@@ -896,10 +896,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>45</v>
@@ -916,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95AA517-A307-2B4E-89E5-0D548B37372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A4BBC4-4F61-4437-9687-4475EE1D81D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5860" windowWidth="28040" windowHeight="10920" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15225" activeTab="4" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Infrastructure" sheetId="1" r:id="rId1"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId2"/>
     <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId3"/>
     <sheet name="Infrastructure (2)" sheetId="4" r:id="rId4"/>
+    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId5"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="28">
   <si>
     <t>type</t>
   </si>
@@ -509,12 +511,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +533,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -551,7 +553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -571,7 +573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -591,7 +593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -611,7 +613,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -639,9 +641,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -661,7 +663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -681,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -701,7 +703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -721,7 +723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -741,7 +743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -761,7 +763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -781,7 +783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -801,7 +803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -821,7 +823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -841,7 +843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -869,9 +871,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -891,7 +893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -911,7 +913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -939,12 +941,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -961,7 +963,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -981,7 +983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1001,14 +1003,299 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I6" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A4BBC4-4F61-4437-9687-4475EE1D81D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1D9AE8-356C-4FB3-A582-6B5BFF338217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15225" activeTab="4" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15225" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Infrastructure" sheetId="1" r:id="rId1"/>
-    <sheet name="PassengerGroups" sheetId="2" r:id="rId2"/>
-    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId3"/>
-    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId4"/>
-    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId5"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId6"/>
+    <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
+    <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
+    <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId4"/>
+    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId5"/>
+    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId6"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
   <si>
     <t>type</t>
   </si>
@@ -125,6 +126,12 @@
   </si>
   <si>
     <t>(37.4875, 127.1013)</t>
+  </si>
+  <si>
+    <t>Plane ID</t>
+  </si>
+  <si>
+    <t>Base Vertiport</t>
   </si>
 </sst>
 </file>
@@ -509,6 +516,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -638,7 +698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -868,7 +928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -938,7 +998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1017,7 +1077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1132,7 +1192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C1D9AE8-356C-4FB3-A582-6B5BFF338217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1877C7-F185-4351-8A8C-B51DCD0446C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15225" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -138,7 +138,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -157,6 +157,11 @@
       <color rgb="FF0A0A0A"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="CharisSIL"/>
     </font>
   </fonts>
   <fills count="2">
@@ -179,10 +184,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,7 +708,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -922,6 +930,320 @@
       <c r="F11">
         <v>1</v>
       </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>50</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>65</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>90</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>60</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1877C7-F185-4351-8A8C-B51DCD0446C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3FECCD-FB74-4C43-8F45-40E55A7BCAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="13095" yWindow="8025" windowWidth="18855" windowHeight="10305" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -933,36 +933,36 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -973,39 +973,39 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -1022,50 +1022,50 @@
         <v>4</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1073,19 +1073,19 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1093,21 +1093,41 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20">
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
         <v>4</v>
       </c>
-      <c r="D20">
+      <c r="D21">
         <v>60</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
         <v>0</v>
       </c>
     </row>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,29 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473B2F8-CE9E-DC40-B158-DDACBE492212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7816C04-DD99-0F4D-9593-D4905A02CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="16560" windowHeight="18380" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parameters" sheetId="9" r:id="rId1"/>
-    <sheet name="PlaneData" sheetId="7" r:id="rId2"/>
-    <sheet name="PlaneData (2)" sheetId="8" r:id="rId3"/>
-    <sheet name="Infrastructure" sheetId="1" r:id="rId4"/>
-    <sheet name="PassengerGroups" sheetId="2" r:id="rId5"/>
-    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId6"/>
-    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId7"/>
-    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId8"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId9"/>
+    <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
+    <sheet name="PlaneData (2)" sheetId="8" r:id="rId2"/>
+    <sheet name="Infrastructure" sheetId="1" r:id="rId3"/>
+    <sheet name="PassengerGroups" sheetId="2" r:id="rId4"/>
+    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId5"/>
+    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId6"/>
+    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId7"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
   <si>
     <t>type</t>
   </si>
@@ -52,6 +51,9 @@
     <t>vertiport</t>
   </si>
   <si>
+    <t>vertistop</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -131,94 +133,13 @@
   </si>
   <si>
     <t>Base Vertiport</t>
-  </si>
-  <si>
-    <t>cap_flt</t>
-  </si>
-  <si>
-    <t>cap_u</t>
-  </si>
-  <si>
-    <t>bmax</t>
-  </si>
-  <si>
-    <t>bmin</t>
-  </si>
-  <si>
-    <t>ec</t>
-  </si>
-  <si>
-    <t>te</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>ET</t>
-  </si>
-  <si>
-    <t>fd_{i,j} = $3/km</t>
-  </si>
-  <si>
-    <t>fs_{i,j}=75% of fd_{i,j}</t>
-  </si>
-  <si>
-    <t>p_a = $10</t>
-  </si>
-  <si>
-    <t>c_{i,j} = $1/km</t>
-  </si>
-  <si>
-    <t>e_{i,j} = 1%/km</t>
-  </si>
-  <si>
-    <t>rt_{i,j} = 0.6 min/km</t>
-  </si>
-  <si>
-    <t>capacity of air corridor</t>
-  </si>
-  <si>
-    <t>seat capacity of eVTOL</t>
-  </si>
-  <si>
-    <t>5% battery charged per unit time</t>
-  </si>
-  <si>
-    <t>minimum turnaround time at vertiport</t>
-  </si>
-  <si>
-    <t>maximum waiting time</t>
-  </si>
-  <si>
-    <t>end time</t>
-  </si>
-  <si>
-    <t>fare_stopover_factor</t>
-  </si>
-  <si>
-    <t>p_penalty</t>
-  </si>
-  <si>
-    <t>operating_cost_per_km</t>
-  </si>
-  <si>
-    <t>battery_per_km</t>
-  </si>
-  <si>
-    <t>time_per_km</t>
-  </si>
-  <si>
-    <t>fare_direct_per_km</t>
-  </si>
-  <si>
-    <t>Parameters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -243,6 +164,13 @@
       <color rgb="FF000000"/>
       <name val="CharisSIL"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -264,15 +192,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,179 +533,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="5">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="5">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1.51</v>
-      </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="5">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="5">
-        <v>100</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="5">
-        <v>10</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="5">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="5">
-        <v>10</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="5">
-        <v>10</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="5">
-        <v>240</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -788,10 +542,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -831,8 +585,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31D2D17-FC72-FE49-9329-D197D3094A2B}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
@@ -841,10 +595,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -860,7 +614,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
@@ -881,16 +635,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -904,13 +658,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -924,18 +678,18 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -944,18 +698,18 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -964,18 +718,18 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -984,13 +738,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -998,33 +752,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
-  <cols>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.5" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1111,11 +861,11 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>3</v>
       </c>
       <c r="D6">
         <v>110</v>
@@ -1151,11 +901,11 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
+      <c r="B8" s="4">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
       </c>
       <c r="D8">
         <v>45</v>
@@ -1171,11 +921,11 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
+      <c r="B9" s="4">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -1191,11 +941,11 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
       </c>
       <c r="D10">
         <v>40</v>
@@ -1251,11 +1001,11 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
         <v>5</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
       </c>
       <c r="D13">
         <v>30</v>
@@ -1351,11 +1101,11 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>3</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4">
+        <v>3</v>
       </c>
       <c r="D18">
         <v>65</v>
@@ -1371,11 +1121,11 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4">
         <v>4</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -1411,11 +1161,11 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21">
-        <v>4</v>
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4">
+        <v>3</v>
       </c>
       <c r="D21">
         <v>60</v>
@@ -1566,29 +1316,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1636,7 +1386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
@@ -1649,16 +1399,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1672,13 +1422,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1692,13 +1442,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1708,6 +1458,121 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:11">
+      <c r="I6" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
       <c r="I6" s="1"/>
     </row>
   </sheetData>
@@ -1716,161 +1581,28 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
-  <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7816C04-DD99-0F4D-9593-D4905A02CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473B2F8-CE9E-DC40-B158-DDACBE492212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="16560" windowHeight="18380" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
-    <sheet name="PlaneData (2)" sheetId="8" r:id="rId2"/>
-    <sheet name="Infrastructure" sheetId="1" r:id="rId3"/>
-    <sheet name="PassengerGroups" sheetId="2" r:id="rId4"/>
-    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId5"/>
-    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId6"/>
-    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId7"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId8"/>
+    <sheet name="Parameters" sheetId="9" r:id="rId1"/>
+    <sheet name="PlaneData" sheetId="7" r:id="rId2"/>
+    <sheet name="PlaneData (2)" sheetId="8" r:id="rId3"/>
+    <sheet name="Infrastructure" sheetId="1" r:id="rId4"/>
+    <sheet name="PassengerGroups" sheetId="2" r:id="rId5"/>
+    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId6"/>
+    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId7"/>
+    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId8"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
   <si>
     <t>type</t>
   </si>
@@ -51,9 +52,6 @@
     <t>vertiport</t>
   </si>
   <si>
-    <t>vertistop</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -133,13 +131,94 @@
   </si>
   <si>
     <t>Base Vertiport</t>
+  </si>
+  <si>
+    <t>cap_flt</t>
+  </si>
+  <si>
+    <t>cap_u</t>
+  </si>
+  <si>
+    <t>bmax</t>
+  </si>
+  <si>
+    <t>bmin</t>
+  </si>
+  <si>
+    <t>ec</t>
+  </si>
+  <si>
+    <t>te</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>ET</t>
+  </si>
+  <si>
+    <t>fd_{i,j} = $3/km</t>
+  </si>
+  <si>
+    <t>fs_{i,j}=75% of fd_{i,j}</t>
+  </si>
+  <si>
+    <t>p_a = $10</t>
+  </si>
+  <si>
+    <t>c_{i,j} = $1/km</t>
+  </si>
+  <si>
+    <t>e_{i,j} = 1%/km</t>
+  </si>
+  <si>
+    <t>rt_{i,j} = 0.6 min/km</t>
+  </si>
+  <si>
+    <t>capacity of air corridor</t>
+  </si>
+  <si>
+    <t>seat capacity of eVTOL</t>
+  </si>
+  <si>
+    <t>5% battery charged per unit time</t>
+  </si>
+  <si>
+    <t>minimum turnaround time at vertiport</t>
+  </si>
+  <si>
+    <t>maximum waiting time</t>
+  </si>
+  <si>
+    <t>end time</t>
+  </si>
+  <si>
+    <t>fare_stopover_factor</t>
+  </si>
+  <si>
+    <t>p_penalty</t>
+  </si>
+  <si>
+    <t>operating_cost_per_km</t>
+  </si>
+  <si>
+    <t>battery_per_km</t>
+  </si>
+  <si>
+    <t>time_per_km</t>
+  </si>
+  <si>
+    <t>fare_direct_per_km</t>
+  </si>
+  <si>
+    <t>Parameters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -164,13 +243,6 @@
       <color rgb="FF000000"/>
       <name val="CharisSIL"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -192,14 +264,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,6 +606,179 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="5">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5">
+        <v>100</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5">
+        <v>240</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -542,10 +788,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -585,8 +831,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31D2D17-FC72-FE49-9329-D197D3094A2B}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
@@ -595,10 +841,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -614,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -622,7 +868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
@@ -635,16 +881,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -658,13 +904,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -678,18 +924,18 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -698,18 +944,18 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -718,18 +964,18 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
         <v>12</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -738,13 +984,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
         <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -752,29 +998,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -861,11 +1111,11 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3</v>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
       </c>
       <c r="D6">
         <v>110</v>
@@ -901,11 +1151,11 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1</v>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
       </c>
       <c r="D8">
         <v>45</v>
@@ -921,11 +1171,11 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2</v>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -941,11 +1191,11 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2</v>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
       </c>
       <c r="D10">
         <v>40</v>
@@ -1001,11 +1251,11 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
-        <v>2</v>
-      </c>
-      <c r="C13" s="4">
+      <c r="B13">
         <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
       </c>
       <c r="D13">
         <v>30</v>
@@ -1101,11 +1351,11 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4">
-        <v>2</v>
-      </c>
-      <c r="C18" s="4">
-        <v>3</v>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
       </c>
       <c r="D18">
         <v>65</v>
@@ -1121,11 +1371,11 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="4">
-        <v>3</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19">
         <v>4</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -1161,11 +1411,11 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3</v>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
       </c>
       <c r="D21">
         <v>60</v>
@@ -1316,29 +1566,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1386,7 +1636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
@@ -1399,16 +1649,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1422,13 +1672,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1442,13 +1692,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1458,121 +1708,6 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="I6" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
-  <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
       <c r="I6" s="1"/>
     </row>
   </sheetData>
@@ -1581,28 +1716,161 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3FECCD-FB74-4C43-8F45-40E55A7BCAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473B2F8-CE9E-DC40-B158-DDACBE492212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13095" yWindow="8025" windowWidth="18855" windowHeight="10305" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
-    <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
-    <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
-    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId4"/>
-    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId5"/>
-    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId6"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId7"/>
+    <sheet name="Parameters" sheetId="9" r:id="rId1"/>
+    <sheet name="PlaneData" sheetId="7" r:id="rId2"/>
+    <sheet name="PlaneData (2)" sheetId="8" r:id="rId3"/>
+    <sheet name="Infrastructure" sheetId="1" r:id="rId4"/>
+    <sheet name="PassengerGroups" sheetId="2" r:id="rId5"/>
+    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId6"/>
+    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId7"/>
+    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId8"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
   <si>
     <t>type</t>
   </si>
@@ -50,9 +52,6 @@
     <t>vertiport</t>
   </si>
   <si>
-    <t>vertistop</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -132,13 +131,94 @@
   </si>
   <si>
     <t>Base Vertiport</t>
+  </si>
+  <si>
+    <t>cap_flt</t>
+  </si>
+  <si>
+    <t>cap_u</t>
+  </si>
+  <si>
+    <t>bmax</t>
+  </si>
+  <si>
+    <t>bmin</t>
+  </si>
+  <si>
+    <t>ec</t>
+  </si>
+  <si>
+    <t>te</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>ET</t>
+  </si>
+  <si>
+    <t>fd_{i,j} = $3/km</t>
+  </si>
+  <si>
+    <t>fs_{i,j}=75% of fd_{i,j}</t>
+  </si>
+  <si>
+    <t>p_a = $10</t>
+  </si>
+  <si>
+    <t>c_{i,j} = $1/km</t>
+  </si>
+  <si>
+    <t>e_{i,j} = 1%/km</t>
+  </si>
+  <si>
+    <t>rt_{i,j} = 0.6 min/km</t>
+  </si>
+  <si>
+    <t>capacity of air corridor</t>
+  </si>
+  <si>
+    <t>seat capacity of eVTOL</t>
+  </si>
+  <si>
+    <t>5% battery charged per unit time</t>
+  </si>
+  <si>
+    <t>minimum turnaround time at vertiport</t>
+  </si>
+  <si>
+    <t>maximum waiting time</t>
+  </si>
+  <si>
+    <t>end time</t>
+  </si>
+  <si>
+    <t>fare_stopover_factor</t>
+  </si>
+  <si>
+    <t>p_penalty</t>
+  </si>
+  <si>
+    <t>operating_cost_per_km</t>
+  </si>
+  <si>
+    <t>battery_per_km</t>
+  </si>
+  <si>
+    <t>time_per_km</t>
+  </si>
+  <si>
+    <t>fare_direct_per_km</t>
+  </si>
+  <si>
+    <t>Parameters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -184,13 +264,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,51 +606,171 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="5">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>2</v>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5">
+        <v>100</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5">
+        <v>240</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -577,128 +779,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
       <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -707,31 +832,202 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -751,7 +1047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -771,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -791,7 +1087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -811,7 +1107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -831,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -851,7 +1147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -871,7 +1167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -891,7 +1187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -911,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -931,7 +1227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -951,7 +1247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -971,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -991,7 +1287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1011,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1031,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1051,7 +1347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1071,7 +1367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1091,7 +1387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1111,7 +1407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1131,7 +1427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1139,7 +1435,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -1153,7 +1449,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -1167,7 +1463,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1181,7 +1477,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1195,7 +1491,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1209,7 +1505,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1223,7 +1519,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1237,7 +1533,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1251,7 +1547,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -1270,32 +1566,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1315,7 +1611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1334,200 +1630,6 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I6" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1535,31 +1637,243 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="I6" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1579,7 +1893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1599,7 +1913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1619,7 +1933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1639,7 +1953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1659,7 +1973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1679,7 +1993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7473B2F8-CE9E-DC40-B158-DDACBE492212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BEFCBE-2A72-6841-834F-3FB26F9090DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -767,7 +767,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="5">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>48</v>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7816C04-DD99-0F4D-9593-D4905A02CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BEFCBE-2A72-6841-834F-3FB26F9090DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="16560" windowHeight="18380" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
-    <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
-    <sheet name="PlaneData (2)" sheetId="8" r:id="rId2"/>
-    <sheet name="Infrastructure" sheetId="1" r:id="rId3"/>
-    <sheet name="PassengerGroups" sheetId="2" r:id="rId4"/>
-    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId5"/>
-    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId6"/>
-    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId7"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId8"/>
+    <sheet name="Parameters" sheetId="9" r:id="rId1"/>
+    <sheet name="PlaneData" sheetId="7" r:id="rId2"/>
+    <sheet name="PlaneData (2)" sheetId="8" r:id="rId3"/>
+    <sheet name="Infrastructure" sheetId="1" r:id="rId4"/>
+    <sheet name="PassengerGroups" sheetId="2" r:id="rId5"/>
+    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId6"/>
+    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId7"/>
+    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId8"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
   <si>
     <t>type</t>
   </si>
@@ -51,9 +52,6 @@
     <t>vertiport</t>
   </si>
   <si>
-    <t>vertistop</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -133,13 +131,94 @@
   </si>
   <si>
     <t>Base Vertiport</t>
+  </si>
+  <si>
+    <t>cap_flt</t>
+  </si>
+  <si>
+    <t>cap_u</t>
+  </si>
+  <si>
+    <t>bmax</t>
+  </si>
+  <si>
+    <t>bmin</t>
+  </si>
+  <si>
+    <t>ec</t>
+  </si>
+  <si>
+    <t>te</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>ET</t>
+  </si>
+  <si>
+    <t>fd_{i,j} = $3/km</t>
+  </si>
+  <si>
+    <t>fs_{i,j}=75% of fd_{i,j}</t>
+  </si>
+  <si>
+    <t>p_a = $10</t>
+  </si>
+  <si>
+    <t>c_{i,j} = $1/km</t>
+  </si>
+  <si>
+    <t>e_{i,j} = 1%/km</t>
+  </si>
+  <si>
+    <t>rt_{i,j} = 0.6 min/km</t>
+  </si>
+  <si>
+    <t>capacity of air corridor</t>
+  </si>
+  <si>
+    <t>seat capacity of eVTOL</t>
+  </si>
+  <si>
+    <t>5% battery charged per unit time</t>
+  </si>
+  <si>
+    <t>minimum turnaround time at vertiport</t>
+  </si>
+  <si>
+    <t>maximum waiting time</t>
+  </si>
+  <si>
+    <t>end time</t>
+  </si>
+  <si>
+    <t>fare_stopover_factor</t>
+  </si>
+  <si>
+    <t>p_penalty</t>
+  </si>
+  <si>
+    <t>operating_cost_per_km</t>
+  </si>
+  <si>
+    <t>battery_per_km</t>
+  </si>
+  <si>
+    <t>time_per_km</t>
+  </si>
+  <si>
+    <t>fare_direct_per_km</t>
+  </si>
+  <si>
+    <t>Parameters</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -164,13 +243,6 @@
       <color rgb="FF000000"/>
       <name val="CharisSIL"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -192,14 +264,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,6 +606,179 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="5">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5">
+        <v>100</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5">
+        <v>10</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="5">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="5">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="5">
+        <v>300</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
@@ -542,10 +788,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -585,8 +831,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C31D2D17-FC72-FE49-9329-D197D3094A2B}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
@@ -595,10 +841,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -614,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -622,7 +868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
@@ -635,16 +881,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -658,13 +904,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -678,18 +924,18 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -698,18 +944,18 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -718,18 +964,18 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
         <v>12</v>
-      </c>
-      <c r="K5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -738,13 +984,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
         <v>14</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -752,29 +998,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -861,11 +1111,11 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4">
-        <v>3</v>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
       </c>
       <c r="D6">
         <v>110</v>
@@ -901,11 +1151,11 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1</v>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
       </c>
       <c r="D8">
         <v>45</v>
@@ -921,11 +1171,11 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
-        <v>3</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2</v>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
       </c>
       <c r="D9">
         <v>60</v>
@@ -941,11 +1191,11 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2</v>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
       </c>
       <c r="D10">
         <v>40</v>
@@ -1001,11 +1251,11 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
-        <v>2</v>
-      </c>
-      <c r="C13" s="4">
+      <c r="B13">
         <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
       </c>
       <c r="D13">
         <v>30</v>
@@ -1101,11 +1351,11 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4">
-        <v>2</v>
-      </c>
-      <c r="C18" s="4">
-        <v>3</v>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
       </c>
       <c r="D18">
         <v>65</v>
@@ -1121,11 +1371,11 @@
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="4">
-        <v>3</v>
-      </c>
-      <c r="C19" s="4">
+      <c r="B19">
         <v>4</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
       </c>
       <c r="D19">
         <v>90</v>
@@ -1161,11 +1411,11 @@
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="4">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4">
-        <v>3</v>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
       </c>
       <c r="D21">
         <v>60</v>
@@ -1316,29 +1566,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1386,7 +1636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
@@ -1399,16 +1649,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1422,13 +1672,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1442,13 +1692,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1458,121 +1708,6 @@
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="I6" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
-  <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
       <c r="I6" s="1"/>
     </row>
   </sheetData>
@@ -1581,28 +1716,161 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BEFCBE-2A72-6841-834F-3FB26F9090DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CCE681-7DE4-4AB3-BA5C-F8000A0144C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" firstSheet="6" activeTab="8" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -21,9 +21,11 @@
     <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId6"/>
     <sheet name="Infrastructure (2)" sheetId="4" r:id="rId7"/>
     <sheet name="Infrastructure (3)" sheetId="6" r:id="rId8"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId9"/>
+    <sheet name="PassengerGroups (4)" sheetId="11" r:id="rId9"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="56">
   <si>
     <t>type</t>
   </si>
@@ -218,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -608,29 +610,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="5"/>
+    <col min="1" max="1" width="22.75" customWidth="1"/>
+    <col min="2" max="2" width="10.875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B2" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -641,7 +643,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -652,7 +654,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -663,7 +665,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -674,7 +676,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -685,7 +687,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -696,7 +698,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -707,7 +709,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -718,7 +720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -729,7 +731,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -740,7 +742,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -751,7 +753,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -762,7 +764,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -774,6 +776,185 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -781,12 +962,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -794,7 +975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -802,7 +983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -810,7 +991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -818,7 +999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -833,13 +1014,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -847,7 +1028,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -855,12 +1036,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -871,12 +1060,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -893,7 +1082,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -913,7 +1102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -933,7 +1122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -953,7 +1142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -973,7 +1162,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1001,13 +1190,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1027,7 +1216,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1046,8 +1235,12 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="J2">
+        <f ca="1">RANDBETWEEN(10,300)</f>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1067,7 +1260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1087,7 +1280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1107,7 +1300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1127,7 +1320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1147,7 +1340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1167,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1187,7 +1380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1207,7 +1400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1227,7 +1420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1247,7 +1440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1267,7 +1460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1287,7 +1480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1307,7 +1500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1327,7 +1520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1347,7 +1540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1367,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1387,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1407,7 +1600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1427,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1435,7 +1628,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -1449,7 +1642,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -1463,7 +1656,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1477,7 +1670,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1491,7 +1684,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1505,7 +1698,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1519,7 +1712,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1533,7 +1726,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1547,7 +1740,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -1569,9 +1762,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1591,7 +1784,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1611,7 +1804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1639,12 +1832,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1661,7 +1854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1681,7 +1874,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1701,13 +1894,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I6" s="1"/>
     </row>
   </sheetData>
@@ -1718,14 +1911,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1742,7 +1935,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1762,7 +1955,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1782,7 +1975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1802,7 +1995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1822,7 +2015,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1849,11 +2042,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
+  <dimension ref="A1:X32"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1873,7 +2070,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1884,28 +2081,30 @@
         <v>3</v>
       </c>
       <c r="D2">
+        <f ca="1">RANDBETWEEN(10,300)</f>
+        <v>117</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D20" ca="1" si="0">RANDBETWEEN(10,300)</f>
         <v>25</v>
       </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>50</v>
-      </c>
       <c r="E3">
         <v>3</v>
       </c>
@@ -1913,7 +2112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1924,16 +2123,17 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>70</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1941,19 +2141,20 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>156</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1964,7 +2165,8 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>110</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1973,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1984,7 +2186,8 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>76</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1993,7 +2196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2004,7 +2207,8 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>217</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2012,6 +2216,413 @@
       <c r="F8">
         <v>1</v>
       </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ca="1" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ca="1" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ca="1" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ca="1" si="0"/>
+        <v>174</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ca="1" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ca="1" si="0"/>
+        <v>168</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ca="1" si="0"/>
+        <v>205</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ca="1" si="0"/>
+        <v>245</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ca="1" si="0"/>
+        <v>235</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ca="1" si="0"/>
+        <v>182</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ca="1" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <f ca="1">RANDBETWEEN(10,300)</f>
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CCE681-7DE4-4AB3-BA5C-F8000A0144C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670D6A40-CD53-4036-BC35-D27F4FC351E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" firstSheet="6" activeTab="8" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="55">
   <si>
     <t>type</t>
   </si>
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>fs_{i,j}=75% of fd_{i,j}</t>
-  </si>
-  <si>
-    <t>p_a = $10</t>
   </si>
   <si>
     <t>c_{i,j} = $1/km</t>
@@ -220,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -610,20 +607,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="22.75" customWidth="1"/>
-    <col min="2" max="2" width="10.875" style="5"/>
+    <col min="2" max="2" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="5">
         <v>5</v>
@@ -632,9 +629,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="5">
         <v>0.75</v>
@@ -643,51 +640,51 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="5">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>50</v>
-      </c>
-      <c r="B4" s="5">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>51</v>
       </c>
       <c r="B5" s="5">
         <v>1.51</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5">
         <v>0.3</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="5">
         <v>0.2</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -695,10 +692,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -706,10 +703,10 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -720,7 +717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -731,7 +728,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -739,10 +736,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -750,10 +747,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -761,18 +758,18 @@
         <v>10</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>36</v>
       </c>
       <c r="B15" s="5">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -783,9 +780,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -805,7 +802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -825,7 +822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -845,7 +842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -865,7 +862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -885,7 +882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -905,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -925,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -953,7 +950,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -962,12 +959,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -975,7 +972,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -983,7 +980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -991,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -999,7 +996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1014,13 +1011,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1028,7 +1025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1036,20 +1033,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1060,12 +1049,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1082,7 +1071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1102,7 +1091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1122,7 +1111,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1142,7 +1131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1162,7 +1151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1190,13 +1179,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1216,7 +1205,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1235,12 +1224,8 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <f ca="1">RANDBETWEEN(10,300)</f>
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1260,7 +1245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1280,7 +1265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1300,7 +1285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1320,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1340,7 +1325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1360,7 +1345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1380,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1400,7 +1385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1420,7 +1405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1440,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1460,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1480,7 +1465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1500,7 +1485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1520,7 +1505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1540,7 +1525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1560,7 +1545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1580,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1600,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1620,7 +1605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1628,7 +1613,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -1642,7 +1627,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -1656,7 +1641,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1670,7 +1655,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1684,7 +1669,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1698,7 +1683,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1712,7 +1697,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1726,7 +1711,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1740,7 +1725,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -1762,9 +1747,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1784,7 +1769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1804,7 +1789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1832,12 +1817,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1854,7 +1839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1874,7 +1859,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1894,13 +1879,13 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="I6" s="1"/>
     </row>
   </sheetData>
@@ -1911,14 +1896,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1935,7 +1920,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1955,7 +1940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1975,7 +1960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1995,7 +1980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -2015,7 +2000,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -2044,13 +2029,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2070,7 +2055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2081,8 +2066,8 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <f ca="1">RANDBETWEEN(10,300)</f>
-        <v>117</v>
+        <f ca="1">RANDBETWEEN(10,120)</f>
+        <v>102</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2091,7 +2076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2102,8 +2087,8 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D20" ca="1" si="0">RANDBETWEEN(10,300)</f>
-        <v>25</v>
+        <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
+        <v>115</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2112,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2124,7 +2109,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2133,7 +2118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2145,7 +2130,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2154,7 +2139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2166,7 +2151,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2175,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2187,7 +2172,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2196,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2208,7 +2193,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>217</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2217,7 +2202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2229,7 +2214,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2238,7 +2223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2250,7 +2235,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2259,7 +2244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2271,7 +2256,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>250</v>
+        <v>117</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2280,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2292,7 +2277,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>174</v>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2301,7 +2286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2313,7 +2298,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2322,7 +2307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2334,7 +2319,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2343,7 +2328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2355,7 +2340,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2364,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2376,7 +2361,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>205</v>
+        <v>101</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2385,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2397,7 +2382,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>245</v>
+        <v>66</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2406,7 +2391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2418,7 +2403,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>235</v>
+        <v>61</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2427,7 +2412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2439,7 +2424,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>182</v>
+        <v>69</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2448,7 +2433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2460,7 +2445,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2469,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2480,8 +2465,8 @@
         <v>4</v>
       </c>
       <c r="D21">
-        <f ca="1">RANDBETWEEN(10,300)</f>
-        <v>32</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>101</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2490,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -2498,7 +2483,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -2512,7 +2497,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -2526,7 +2511,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -2540,7 +2525,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -2554,7 +2539,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -2568,7 +2553,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -2582,7 +2567,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -2596,7 +2581,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -2610,7 +2595,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BEFCBE-2A72-6841-834F-3FB26F9090DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670D6A40-CD53-4036-BC35-D27F4FC351E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="10000" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -21,9 +21,11 @@
     <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId6"/>
     <sheet name="Infrastructure (2)" sheetId="4" r:id="rId7"/>
     <sheet name="Infrastructure (3)" sheetId="6" r:id="rId8"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId9"/>
+    <sheet name="PassengerGroups (4)" sheetId="11" r:id="rId9"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="55">
   <si>
     <t>type</t>
   </si>
@@ -161,9 +163,6 @@
   </si>
   <si>
     <t>fs_{i,j}=75% of fd_{i,j}</t>
-  </si>
-  <si>
-    <t>p_a = $10</t>
   </si>
   <si>
     <t>c_{i,j} = $1/km</t>
@@ -608,23 +607,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.75" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -632,7 +631,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="5">
         <v>0.75</v>
@@ -643,46 +642,46 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="5">
         <v>1.51</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5">
         <v>0.3</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="5">
         <v>0.2</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -693,7 +692,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -704,7 +703,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -737,7 +736,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -748,7 +747,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -759,7 +758,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -767,13 +766,192 @@
         <v>36</v>
       </c>
       <c r="B15" s="5">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -781,7 +959,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -834,7 +1012,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -871,9 +1049,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1001,7 +1179,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1569,7 +1747,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1639,9 +1817,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1718,9 +1896,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.58203125" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -1849,9 +2027,13 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
+  <dimension ref="A1:X32"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1884,7 +2066,8 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <f ca="1">RANDBETWEEN(10,120)</f>
+        <v>102</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1904,7 +2087,8 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
+        <v>115</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1924,13 +2108,14 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>70</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>79</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1941,16 +2126,17 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>119</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1964,7 +2150,8 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>110</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1984,7 +2171,8 @@
         <v>3</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>114</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2004,7 +2192,8 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2012,6 +2201,413 @@
       <c r="F8">
         <v>1</v>
       </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ca="1" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <f t="shared" ca="1" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ca="1" si="0"/>
+        <v>117</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ca="1" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ca="1" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ca="1" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ca="1" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ca="1" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ca="1" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>5</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ca="1" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <f t="shared" ca="1" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="1:24">
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670D6A40-CD53-4036-BC35-D27F4FC351E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53581A06-9005-4CD8-98F9-33D5717E39C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" firstSheet="6" activeTab="8" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="56">
   <si>
     <t>type</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Parameters</t>
+  </si>
+  <si>
+    <t>Helper Column</t>
   </si>
 </sst>
 </file>
@@ -2035,7 +2038,7 @@
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2054,20 +2057,25 @@
       <c r="F1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <f ca="1">IF(IF(I2=B2,I2+1,I2) &gt; 5, I2 -1, I2)</f>
+        <v>1</v>
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2075,20 +2083,26 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="I2">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <f t="shared" ref="B3:B21" ca="1" si="0">RANDBETWEEN(1,5)</f>
+        <v>2</v>
       </c>
       <c r="C3">
+        <f t="shared" ref="C3:C21" ca="1" si="1">IF(IF(I3=B3,I3+1,I3) &gt; 5, I3 -1, I3)</f>
         <v>1</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>115</v>
+        <f t="shared" ref="D3:D21" ca="1" si="2">RANDBETWEEN(10,120)</f>
+        <v>77</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2096,41 +2110,53 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="I3">
+        <f t="shared" ref="I3:I21" ca="1" si="3">RANDBETWEEN(1,5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
       </c>
       <c r="D4">
+        <f t="shared" ca="1" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="D5">
-        <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2138,20 +2164,26 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="I5">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="C6">
+        <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
       <c r="D6">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>50</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2159,20 +2191,26 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="I6">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
       </c>
       <c r="D7">
-        <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>88</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2180,20 +2218,26 @@
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="I7">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
       </c>
       <c r="D8">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2201,20 +2245,26 @@
       <c r="F8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="I8">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="D9">
-        <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2222,20 +2272,26 @@
       <c r="F9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="I9">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
       </c>
       <c r="D10">
-        <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>113</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2243,20 +2299,26 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="I10">
+        <f t="shared" ca="1" si="3"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
       </c>
       <c r="D11">
-        <f t="shared" ca="1" si="0"/>
-        <v>117</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>109</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2264,20 +2326,26 @@
       <c r="F11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="I11">
+        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
+        <f t="shared" ca="1" si="0"/>
         <v>1</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="D12">
-        <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2285,20 +2353,26 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="I12">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
       <c r="C13">
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
       <c r="D13">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>62</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2306,19 +2380,25 @@
       <c r="F13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="I13">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
+        <f t="shared" ca="1" si="0"/>
         <v>3</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="D14">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" ca="1" si="2"/>
         <v>62</v>
       </c>
       <c r="E14">
@@ -2327,20 +2407,26 @@
       <c r="F14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="I14">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="D15">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>18</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2348,26 +2434,36 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="I15">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="C16">
+        <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
       <c r="D16">
-        <f t="shared" ca="1" si="0"/>
-        <v>101</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>24</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16">
         <v>0</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2375,20 +2471,26 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
       </c>
       <c r="D17">
-        <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>53</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
         <v>1</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2396,20 +2498,26 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
       </c>
       <c r="D18">
-        <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>99</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
         <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2417,20 +2525,26 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>2</v>
       </c>
       <c r="C19">
+        <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
       <c r="D19">
-        <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>115</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
         <v>0</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2438,20 +2552,26 @@
         <v>19</v>
       </c>
       <c r="B20">
+        <f t="shared" ca="1" si="0"/>
         <v>5</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
       </c>
       <c r="D20">
-        <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>49</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
         <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" ca="1" si="3"/>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2459,20 +2579,26 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
       </c>
       <c r="D21">
-        <f t="shared" ca="1" si="0"/>
-        <v>101</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>102</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
         <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" ca="1" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53581A06-9005-4CD8-98F9-33D5717E39C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184B500-CFA4-415D-972C-97C389BBF879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="11260" firstSheet="6" activeTab="8" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -648,7 +648,7 @@
         <v>49</v>
       </c>
       <c r="B4" s="5">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="D4" t="s">
         <v>43</v>
@@ -747,7 +747,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>45</v>
@@ -758,7 +758,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>46</v>
@@ -2038,7 +2038,7 @@
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2061,21 +2061,19 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <f ca="1">IF(IF(I2=B2,I2+1,I2) &gt; 5, I2 -1, I2)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2087,22 +2085,28 @@
         <f ca="1">RANDBETWEEN(1,5)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="K2">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B21" ca="1" si="0">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C21" ca="1" si="1">IF(IF(I3=B3,I3+1,I3) &gt; 5, I3 -1, I3)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D21" ca="1" si="2">RANDBETWEEN(10,120)</f>
-        <v>77</v>
+        <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2111,359 +2115,445 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I21" ca="1" si="3">RANDBETWEEN(1,5)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C4">
+        <v>101</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ca="1" si="2"/>
-        <v>44</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <f t="shared" ca="1" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C5">
+        <v>114</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <f t="shared" ca="1" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C6">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <f t="shared" ca="1" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <f t="shared" ca="1" si="2"/>
-        <v>88</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <f t="shared" ca="1" si="3"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <f t="shared" ca="1" si="1"/>
         <v>2</v>
       </c>
-      <c r="D8">
-        <f t="shared" ca="1" si="2"/>
-        <v>84</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <f t="shared" ca="1" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="K8">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C9">
+        <v>74</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <f t="shared" ca="1" si="2"/>
-        <v>19</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C10">
+        <v>102</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <f t="shared" ca="1" si="2"/>
-        <v>113</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <f t="shared" ca="1" si="3"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C11">
+        <v>78</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="D11">
-        <f t="shared" ca="1" si="2"/>
-        <v>109</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <f t="shared" ca="1" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>5</v>
+      </c>
+      <c r="K11">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C12">
+        <v>89</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <f t="shared" ca="1" si="2"/>
-        <v>26</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>4</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C13">
+        <v>74</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <f t="shared" ca="1" si="2"/>
-        <v>62</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <f t="shared" ca="1" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>4</v>
+      </c>
+      <c r="K13">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C14">
+        <v>24</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <f t="shared" ca="1" si="2"/>
-        <v>62</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C15">
+        <v>42</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <f t="shared" ca="1" si="1"/>
         <v>1</v>
       </c>
-      <c r="D15">
-        <f t="shared" ca="1" si="2"/>
-        <v>18</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="K15">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C16">
+        <v>31</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="D16">
-        <f t="shared" ca="1" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2471,26 +2561,32 @@
         <v>16</v>
       </c>
       <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C17">
+        <v>91</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <f t="shared" ca="1" si="2"/>
-        <v>53</v>
-      </c>
-      <c r="E17">
-        <v>3</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <f t="shared" ca="1" si="3"/>
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2498,26 +2594,32 @@
         <v>17</v>
       </c>
       <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C18">
+        <v>21</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <f t="shared" ca="1" si="2"/>
-        <v>99</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="K18">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2525,25 +2627,31 @@
         <v>18</v>
       </c>
       <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="C19">
+        <v>53</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="D19">
-        <f t="shared" ca="1" si="2"/>
-        <v>115</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <f t="shared" ca="1" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="K19">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -2552,26 +2660,32 @@
         <v>19</v>
       </c>
       <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C20">
+        <v>44</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <f t="shared" ca="1" si="1"/>
         <v>4</v>
       </c>
-      <c r="D20">
-        <f t="shared" ca="1" si="2"/>
-        <v>49</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <f t="shared" ca="1" si="3"/>
-        <v>4</v>
+      <c r="K20">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2579,26 +2693,32 @@
         <v>20</v>
       </c>
       <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C21">
+        <v>23</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <f t="shared" ca="1" si="2"/>
-        <v>102</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <f t="shared" ca="1" si="3"/>
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K21">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F184B500-CFA4-415D-972C-97C389BBF879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65564938-94FB-44AE-953A-A74912A52C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -1014,7 +1014,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -1042,6 +1042,14 @@
       </c>
       <c r="B3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2081,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2083,15 +2091,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2116,15 +2124,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2139,7 +2147,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2149,15 +2157,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2172,7 +2180,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2182,7 +2190,7 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
@@ -2190,7 +2198,7 @@
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2205,7 +2213,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2215,11 +2223,11 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
@@ -2238,7 +2246,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2248,15 +2256,15 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2271,7 +2279,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2281,11 +2289,11 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
@@ -2304,7 +2312,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2314,15 +2322,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2337,7 +2345,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2347,11 +2355,11 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
@@ -2370,7 +2378,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2380,11 +2388,11 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
@@ -2403,7 +2411,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2421,7 +2429,7 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2436,7 +2444,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2446,15 +2454,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2469,7 +2477,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2483,11 +2491,11 @@
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2502,7 +2510,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2512,7 +2520,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
@@ -2520,7 +2528,7 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2535,7 +2543,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2545,11 +2553,11 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
@@ -2568,7 +2576,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2578,15 +2586,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2601,7 +2609,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2611,11 +2619,11 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
@@ -2634,7 +2642,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2644,15 +2652,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2667,7 +2675,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2677,15 +2685,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2700,7 +2708,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2710,15 +2718,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65564938-94FB-44AE-953A-A74912A52C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2091,11 +2091,11 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2124,15 +2124,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2157,15 +2157,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2190,11 +2190,11 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2223,15 +2223,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2256,15 +2256,15 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2289,15 +2289,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2355,15 +2355,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2388,11 +2388,11 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2425,11 +2425,11 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2454,11 +2454,11 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2487,15 +2487,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2553,15 +2553,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
-      </c>
-      <c r="L16">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2586,15 +2586,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2652,15 +2652,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2685,11 +2685,11 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\HanSong_Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65564938-94FB-44AE-953A-A74912A52C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061662BB-0E5B-294D-B053-1AE9ADF04472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="7" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -610,9 +610,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="22.75" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
@@ -783,7 +783,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -953,7 +953,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -962,7 +962,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1015,7 +1015,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1060,9 +1060,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1190,7 +1190,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1758,7 +1758,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1828,9 +1828,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1907,9 +1907,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.58203125" customWidth="1"/>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
     <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -1979,7 +1979,7 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
@@ -2019,7 +2019,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -2040,7 +2040,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2091,11 +2091,11 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2124,15 +2124,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2157,15 +2157,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2256,11 +2256,11 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2388,15 +2388,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2454,15 +2454,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2491,11 +2491,11 @@
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2553,15 +2553,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2586,15 +2586,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2619,15 +2619,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>61</v>
+        <v>117</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2685,15 +2685,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061662BB-0E5B-294D-B053-1AE9ADF04472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921D0EB5-B4DB-D54D-8549-A4D30041B894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="7" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -769,7 +769,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="5">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>47</v>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2091,11 +2091,11 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2157,15 +2157,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2190,15 +2190,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2223,15 +2223,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2256,15 +2256,15 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2289,15 +2289,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2355,15 +2355,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2421,11 +2421,11 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2454,15 +2454,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2491,11 +2491,11 @@
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2553,15 +2553,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2590,11 +2590,11 @@
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2619,11 +2619,11 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2652,15 +2652,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
-      </c>
-      <c r="L19">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2685,15 +2685,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
-      </c>
-      <c r="K20">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="L20">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2718,11 +2718,11 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921D0EB5-B4DB-D54D-8549-A4D30041B894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADCB5AC-E422-B84E-A036-C1ED4BE57E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1184,6 +1184,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2081,7 +2082,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2091,15 +2092,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2124,15 +2125,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2147,7 +2148,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2157,15 +2158,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2180,7 +2181,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2194,11 +2195,11 @@
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2213,7 +2214,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2223,15 +2224,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2246,7 +2247,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2256,11 +2257,11 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -2279,7 +2280,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2289,15 +2290,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2312,7 +2313,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2322,7 +2323,7 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -2330,7 +2331,7 @@
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2345,7 +2346,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2359,11 +2360,11 @@
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2378,7 +2379,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2388,15 +2389,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2411,7 +2412,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2421,15 +2422,15 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2444,7 +2445,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2454,11 +2455,11 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
@@ -2477,7 +2478,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2487,15 +2488,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2510,7 +2511,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2520,15 +2521,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2543,7 +2544,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2557,11 +2558,11 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2576,7 +2577,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2590,11 +2591,11 @@
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2609,7 +2610,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2619,15 +2620,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2642,7 +2643,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2652,7 +2653,7 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
@@ -2660,7 +2661,7 @@
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2675,7 +2676,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2685,15 +2686,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2708,7 +2709,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2718,15 +2719,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADCB5AC-E422-B84E-A036-C1ED4BE57E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEC886E-388B-1E48-A672-169D8DD898BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" firstSheet="1" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="56">
   <si>
     <t>type</t>
   </si>
@@ -1059,13 +1059,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1076,13 +1076,10 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1092,17 +1089,14 @@
       <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1112,17 +1106,14 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1132,17 +1123,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" t="s">
+      <c r="F4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1152,17 +1140,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K5" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1172,13 +1157,10 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K6" t="s">
+      <c r="F6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2082,7 +2064,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2092,15 +2074,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2115,7 +2097,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2125,7 +2107,7 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
@@ -2133,7 +2115,7 @@
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2148,7 +2130,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2162,11 +2144,11 @@
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2181,7 +2163,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2191,15 +2173,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2214,7 +2196,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2224,7 +2206,7 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
@@ -2232,7 +2214,7 @@
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2247,7 +2229,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2257,7 +2239,7 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
@@ -2265,7 +2247,7 @@
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2280,7 +2262,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2290,11 +2272,11 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
@@ -2313,7 +2295,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2323,15 +2305,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2346,7 +2328,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2356,15 +2338,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2379,7 +2361,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2393,11 +2375,11 @@
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2412,7 +2394,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2422,7 +2404,7 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
@@ -2430,7 +2412,7 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2445,7 +2427,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2455,11 +2437,11 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
@@ -2478,7 +2460,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2492,11 +2474,11 @@
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2511,7 +2493,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2521,7 +2503,7 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
@@ -2529,7 +2511,7 @@
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2544,7 +2526,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2554,15 +2536,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2577,7 +2559,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2587,11 +2569,11 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
@@ -2610,7 +2592,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2620,15 +2602,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2643,7 +2625,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2653,11 +2635,11 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
@@ -2676,7 +2658,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2686,15 +2668,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2709,7 +2691,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2719,15 +2701,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEC886E-388B-1E48-A672-169D8DD898BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F97EC6-1BA1-644D-998B-62DCBE02929F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" firstSheet="1" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -714,7 +714,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -725,7 +725,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4">
         <v>0.1</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2111,11 +2111,11 @@
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2140,15 +2140,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2173,11 +2173,11 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2206,15 +2206,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2239,15 +2239,15 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2272,15 +2272,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2338,15 +2338,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2437,15 +2437,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2503,15 +2503,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2536,15 +2536,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2569,15 +2569,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2602,15 +2602,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2672,11 +2672,11 @@
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2701,15 +2701,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEC886E-388B-1E48-A672-169D8DD898BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368232C9-21AA-1643-A276-3DFA06DE0B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" firstSheet="1" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="9" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2140,15 +2140,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2173,15 +2173,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2206,15 +2206,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2272,15 +2272,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2305,15 +2305,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2342,11 +2342,11 @@
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2371,11 +2371,11 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2441,11 +2441,11 @@
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2470,15 +2470,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2507,11 +2507,11 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2536,11 +2536,11 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2573,11 +2573,11 @@
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2602,15 +2602,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2668,15 +2668,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2701,15 +2701,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368232C9-21AA-1643-A276-3DFA06DE0B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD53209F-D117-C94A-9367-565323C1819E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="9" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -714,7 +714,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -725,7 +725,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4">
         <v>0.1</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2107,15 +2107,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2140,15 +2140,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2206,15 +2206,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2243,11 +2243,11 @@
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2276,11 +2276,11 @@
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2305,15 +2305,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2338,15 +2338,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2371,15 +2371,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2408,11 +2408,11 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2437,11 +2437,11 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2470,15 +2470,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2503,15 +2503,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2536,11 +2536,11 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
-      </c>
-      <c r="K16">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2569,11 +2569,11 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2602,15 +2602,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2635,15 +2635,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
-      </c>
-      <c r="K19">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L19">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2668,15 +2668,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD53209F-D117-C94A-9367-565323C1819E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0050A128-367E-6947-AFF1-621591FD31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -717,7 +717,7 @@
         <v>80</v>
       </c>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,7 +728,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2074,11 +2074,11 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2144,11 +2144,11 @@
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2173,11 +2173,11 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2206,15 +2206,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2239,11 +2239,11 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2272,15 +2272,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2305,15 +2305,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2338,15 +2338,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2437,15 +2437,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2470,15 +2470,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2507,11 +2507,11 @@
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2536,15 +2536,15 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2569,15 +2569,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2668,15 +2668,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2701,15 +2701,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0050A128-367E-6947-AFF1-621591FD31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148DF50B-1AEA-FF44-B3C8-19FBE34AE74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
-    <sheet name="PlaneData" sheetId="7" r:id="rId2"/>
-    <sheet name="PlaneData (2)" sheetId="8" r:id="rId3"/>
-    <sheet name="Infrastructure" sheetId="1" r:id="rId4"/>
-    <sheet name="PassengerGroups" sheetId="2" r:id="rId5"/>
-    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId6"/>
-    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId7"/>
-    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId8"/>
-    <sheet name="PassengerGroups (4)" sheetId="11" r:id="rId9"/>
-    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId11"/>
+    <sheet name="Prices" sheetId="12" r:id="rId2"/>
+    <sheet name="PlaneData" sheetId="7" r:id="rId3"/>
+    <sheet name="PlaneData (2)" sheetId="8" r:id="rId4"/>
+    <sheet name="Infrastructure" sheetId="1" r:id="rId5"/>
+    <sheet name="PassengerGroups" sheetId="2" r:id="rId6"/>
+    <sheet name="PassengerGroups (2)" sheetId="3" r:id="rId7"/>
+    <sheet name="Infrastructure (2)" sheetId="4" r:id="rId8"/>
+    <sheet name="Infrastructure (3)" sheetId="6" r:id="rId9"/>
+    <sheet name="PassengerGroups (4)" sheetId="11" r:id="rId10"/>
+    <sheet name="PassengerGroups (3)" sheetId="5" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="73">
   <si>
     <t>type</t>
   </si>
@@ -214,13 +215,68 @@
   </si>
   <si>
     <t>Helper Column</t>
+  </si>
+  <si>
+    <t>Bil tid (min)</t>
+  </si>
+  <si>
+    <t>Km fugleflugt</t>
+  </si>
+  <si>
+    <t>eVTOL flyvetid (min)</t>
+  </si>
+  <si>
+    <t>Hvor meget hurtigere</t>
+  </si>
+  <si>
+    <t>Fd km</t>
+  </si>
+  <si>
+    <t>Fd tid</t>
+  </si>
+  <si>
+    <t>fd max</t>
+  </si>
+  <si>
+    <t>Passager km pris</t>
+  </si>
+  <si>
+    <t>kr/km</t>
+  </si>
+  <si>
+    <t>Tidsværdi</t>
+  </si>
+  <si>
+    <t>kr/min</t>
+  </si>
+  <si>
+    <t>Lambda</t>
+  </si>
+  <si>
+    <t>Base fee</t>
+  </si>
+  <si>
+    <t>kr</t>
+  </si>
+  <si>
+    <t>From</t>
+  </si>
+  <si>
+    <t>To</t>
+  </si>
+  <si>
+    <t>fd_sum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -245,6 +301,27 @@
       <color rgb="FF000000"/>
       <name val="CharisSIL"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -263,10 +340,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -275,8 +353,28 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -717,7 +815,7 @@
         <v>80</v>
       </c>
       <c r="D10" s="4">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,7 +826,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -781,397 +879,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>25</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>50</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>70</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>40</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>110</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>45</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
-  <cols>
-    <col min="3" max="3" width="22.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
   <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
@@ -1179,7 +887,7 @@
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1198,19 +906,23 @@
       <c r="F1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>45</v>
+        <f ca="1">RANDBETWEEN(10,120)</f>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1218,19 +930,32 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="I2">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <f ca="1">RANDBETWEEN(1,5)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>80</v>
+        <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
+        <v>63</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1238,8 +963,20 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="I3">
+        <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1247,10 +984,11 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>68</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1258,8 +996,20 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="I4">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1270,7 +1020,8 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>70</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1278,19 +1029,32 @@
       <c r="F5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="I5">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>110</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>63</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1298,19 +1062,32 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="I6">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>50</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1318,19 +1095,32 @@
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="I7">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K7">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L7">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8">
-        <v>45</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1338,19 +1128,32 @@
       <c r="F8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="I8">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>60</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>43</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1358,19 +1161,32 @@
       <c r="F9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="I9">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L9">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>95</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1378,39 +1194,65 @@
       <c r="F10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="I10">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ca="1" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <f t="shared" ca="1" si="1"/>
         <v>5</v>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>50</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="K11">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>29</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1418,19 +1260,32 @@
       <c r="F12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="I12">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L12">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>5</v>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
       <c r="D13">
-        <v>30</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1438,19 +1293,32 @@
       <c r="F13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="I13">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1458,19 +1326,32 @@
       <c r="F14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="I14">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L14">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>50</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>62</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1478,25 +1359,50 @@
       <c r="F15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="I15">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L15">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>87</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16">
         <v>0</v>
+      </c>
+      <c r="I16">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ca="1" si="2"/>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1504,19 +1410,32 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>94</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
         <v>1</v>
+      </c>
+      <c r="I17">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K17">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L17">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1524,19 +1443,32 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18">
-        <v>65</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>72</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
         <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K18">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -1544,19 +1476,32 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>68</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
         <v>0</v>
+      </c>
+      <c r="I19">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K19">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -1564,19 +1509,32 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>15</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>94</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
         <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K20">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -1584,19 +1542,32 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>60</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>118</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
         <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K21">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L21">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -1738,10 +1709,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
-  <dimension ref="A1:F3"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1768,13 +1742,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -1788,19 +1762,119 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>110</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1808,96 +1882,729 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332D5C3C-A1DF-48A5-A3F8-29AFDB8C103D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF0D5EA-53B5-1240-9D84-6FE223856A18}">
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
+      <c r="A1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10">
+        <v>2</v>
+      </c>
+      <c r="C2" s="10">
+        <f>(180)</f>
+        <v>180</v>
+      </c>
+      <c r="D2" s="10">
+        <v>219</v>
+      </c>
+      <c r="E2" s="10">
+        <f t="shared" ref="E2:E11" si="0">$M$1*D2</f>
+        <v>43.800000000000004</v>
+      </c>
+      <c r="F2" s="11">
+        <f>C2/E2</f>
+        <v>4.10958904109589</v>
+      </c>
+      <c r="G2" s="12">
+        <f t="shared" ref="G2:G11" si="1">D2*$M$2</f>
+        <v>4161</v>
+      </c>
+      <c r="H2" s="13">
+        <f t="shared" ref="H2:H11" si="2">(C2-E2)*$M$3*$M$4</f>
+        <v>1589</v>
+      </c>
+      <c r="I2" s="13">
+        <f>G2+H2</f>
+        <v>5750</v>
+      </c>
+      <c r="J2" s="13">
+        <f t="shared" ref="J2:J11" si="3">MAX($M$2*D2+$M$5,$M$4*$M$3*(C2-E2))</f>
+        <v>4161</v>
+      </c>
+      <c r="L2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M2" s="5">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10">
+        <v>3</v>
+      </c>
+      <c r="C3" s="10">
+        <v>60</v>
+      </c>
+      <c r="D3" s="10">
+        <v>88</v>
+      </c>
+      <c r="E3" s="10">
+        <f t="shared" si="0"/>
+        <v>17.600000000000001</v>
+      </c>
+      <c r="F3" s="11">
+        <f t="shared" ref="F3:F11" si="4">C3/E3</f>
+        <v>3.4090909090909087</v>
+      </c>
+      <c r="G3" s="12">
+        <f t="shared" si="1"/>
+        <v>1672</v>
+      </c>
+      <c r="H3" s="13">
+        <f t="shared" si="2"/>
+        <v>494.66666666666669</v>
+      </c>
+      <c r="I3" s="13">
+        <f t="shared" ref="I3:I11" si="5">G3+H3</f>
+        <v>2166.6666666666665</v>
+      </c>
+      <c r="J3" s="13">
+        <f t="shared" si="3"/>
+        <v>1672</v>
+      </c>
+      <c r="L3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="5">
+        <f>1000/60</f>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="N3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10">
+        <v>4</v>
+      </c>
+      <c r="C4" s="10">
+        <f>200</f>
+        <v>200</v>
+      </c>
+      <c r="D4" s="10">
+        <v>147</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" si="0"/>
+        <v>29.400000000000002</v>
+      </c>
+      <c r="F4" s="11">
+        <f t="shared" si="4"/>
+        <v>6.8027210884353737</v>
+      </c>
+      <c r="G4" s="12">
+        <f t="shared" si="1"/>
+        <v>2793</v>
+      </c>
+      <c r="H4" s="13">
+        <f t="shared" si="2"/>
+        <v>1990.3333333333333</v>
+      </c>
+      <c r="I4" s="13">
+        <f t="shared" si="5"/>
+        <v>4783.333333333333</v>
+      </c>
+      <c r="J4" s="13">
+        <f t="shared" si="3"/>
+        <v>2793</v>
+      </c>
+      <c r="L4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="10">
+        <v>5</v>
+      </c>
+      <c r="C5" s="10">
+        <f>(60+50)</f>
+        <v>110</v>
+      </c>
+      <c r="D5" s="10">
+        <v>147</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" si="0"/>
+        <v>29.400000000000002</v>
+      </c>
+      <c r="F5" s="11">
+        <f t="shared" si="4"/>
+        <v>3.7414965986394555</v>
+      </c>
+      <c r="G5" s="12">
+        <f t="shared" si="1"/>
+        <v>2793</v>
+      </c>
+      <c r="H5" s="13">
+        <f t="shared" si="2"/>
+        <v>940.33333333333326</v>
+      </c>
+      <c r="I5" s="13">
+        <f t="shared" si="5"/>
+        <v>3733.333333333333</v>
+      </c>
+      <c r="J5" s="13">
+        <f t="shared" si="3"/>
+        <v>2793</v>
+      </c>
+      <c r="L5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="10">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10">
+        <f>(120+40)</f>
+        <v>160</v>
+      </c>
+      <c r="D6" s="10">
+        <v>131</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" si="0"/>
+        <v>26.200000000000003</v>
+      </c>
+      <c r="F6" s="11">
+        <f t="shared" si="4"/>
+        <v>6.1068702290076331</v>
+      </c>
+      <c r="G6" s="12">
+        <f t="shared" si="1"/>
+        <v>2489</v>
+      </c>
+      <c r="H6" s="13">
+        <f t="shared" si="2"/>
+        <v>1561.0000000000002</v>
+      </c>
+      <c r="I6" s="13">
+        <f t="shared" si="5"/>
+        <v>4050</v>
+      </c>
+      <c r="J6" s="13">
+        <f t="shared" si="3"/>
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10">
+        <v>4</v>
+      </c>
+      <c r="C7" s="10">
+        <f>90</f>
+        <v>90</v>
+      </c>
+      <c r="D7" s="10">
+        <v>111</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="0"/>
+        <v>22.200000000000003</v>
+      </c>
+      <c r="F7" s="11">
+        <f t="shared" si="4"/>
+        <v>4.0540540540540535</v>
+      </c>
+      <c r="G7" s="12">
+        <f t="shared" si="1"/>
+        <v>2109</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" si="2"/>
+        <v>791</v>
+      </c>
+      <c r="I7" s="13">
+        <f t="shared" si="5"/>
+        <v>2900</v>
+      </c>
+      <c r="J7" s="13">
+        <f t="shared" si="3"/>
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="10">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10">
+        <f>75</f>
+        <v>75</v>
+      </c>
+      <c r="D8" s="10">
+        <v>80</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="F8" s="11">
+        <f t="shared" si="4"/>
+        <v>4.6875</v>
+      </c>
+      <c r="G8" s="12">
+        <f t="shared" si="1"/>
+        <v>1520</v>
+      </c>
+      <c r="H8" s="13">
+        <f t="shared" si="2"/>
+        <v>688.33333333333337</v>
+      </c>
+      <c r="I8" s="13">
+        <f t="shared" si="5"/>
+        <v>2208.3333333333335</v>
+      </c>
+      <c r="J8" s="13">
+        <f t="shared" si="3"/>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" s="10">
+        <v>4</v>
+      </c>
+      <c r="C9" s="10">
+        <v>180</v>
+      </c>
+      <c r="D9" s="10">
+        <v>79</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="0"/>
+        <v>15.8</v>
+      </c>
+      <c r="F9" s="11">
+        <f t="shared" si="4"/>
+        <v>11.39240506329114</v>
+      </c>
+      <c r="G9" s="12">
+        <f t="shared" si="1"/>
+        <v>1501</v>
+      </c>
+      <c r="H9" s="13">
+        <f t="shared" si="2"/>
+        <v>1915.6666666666665</v>
+      </c>
+      <c r="I9" s="13">
+        <f t="shared" si="5"/>
+        <v>3416.6666666666665</v>
+      </c>
+      <c r="J9" s="13">
+        <f t="shared" si="3"/>
+        <v>1915.6666666666665</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" s="10">
+        <v>5</v>
+      </c>
+      <c r="C10" s="10">
+        <v>90</v>
+      </c>
+      <c r="D10" s="10">
+        <v>63</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="0"/>
+        <v>12.600000000000001</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="4"/>
+        <v>7.1428571428571423</v>
+      </c>
+      <c r="G10" s="12">
+        <f t="shared" si="1"/>
+        <v>1197</v>
+      </c>
+      <c r="H10" s="13">
+        <f t="shared" si="2"/>
+        <v>903.00000000000011</v>
+      </c>
+      <c r="I10" s="13">
+        <f t="shared" si="5"/>
+        <v>2100</v>
+      </c>
+      <c r="J10" s="13">
+        <f t="shared" si="3"/>
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" s="10">
+        <v>5</v>
+      </c>
+      <c r="C11" s="10">
+        <v>120</v>
+      </c>
+      <c r="D11" s="10">
+        <v>93</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="0"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="4"/>
+        <v>6.4516129032258061</v>
+      </c>
+      <c r="G11" s="12">
+        <f t="shared" si="1"/>
+        <v>1767</v>
+      </c>
+      <c r="H11" s="13">
+        <f t="shared" si="2"/>
+        <v>1183</v>
+      </c>
+      <c r="I11" s="13">
+        <f t="shared" si="5"/>
+        <v>2950</v>
+      </c>
+      <c r="J11" s="13">
+        <f t="shared" si="3"/>
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10">
+        <v>1</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="12"/>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" s="10">
+        <v>2</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14">
+        <v>3</v>
+      </c>
+      <c r="B14" s="10">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" s="10">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" s="10">
+        <v>5</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G2:G11">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H11">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J11">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>1</v>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="I6" s="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
-  <dimension ref="A1:G6"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A48C4B-C23A-0343-9CD4-B20C0FE9227B}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1908,13 +2615,10 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1924,17 +2628,14 @@
       <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1944,17 +2645,14 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1962,19 +2660,16 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G4" t="s">
+      <c r="F4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1982,19 +2677,16 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -2002,17 +2694,20 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" t="s">
+      <c r="F6" t="s">
         <v>14</v>
       </c>
+    </row>
+    <row r="18" spans="4:5">
+      <c r="E18" s="6"/>
+    </row>
+    <row r="20" spans="4:5">
+      <c r="D20" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2020,8 +2715,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A73ABDEA-DD83-4C31-B1A2-B93032C8B1F1}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
@@ -2029,7 +2724,7 @@
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2048,23 +2743,19 @@
       <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2072,32 +2763,19 @@
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2105,32 +2783,19 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
         <v>5</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
-        <f t="shared" ca="1" si="0"/>
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2138,20 +2803,8 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="I4">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2162,8 +2815,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2171,32 +2823,19 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="I5">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2204,32 +2843,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="I6">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2237,32 +2863,19 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="I7">
-        <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8">
-        <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2270,32 +2883,19 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="I8">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="K8">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L8">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <f t="shared" ca="1" si="0"/>
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2303,32 +2903,19 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="I9">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="L9">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2336,32 +2923,19 @@
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="I10">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K10">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="L10">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11">
-        <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2369,32 +2943,19 @@
       <c r="F11">
         <v>1</v>
       </c>
-      <c r="I11">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K11">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L11">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12">
-        <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2402,32 +2963,19 @@
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="I12">
-        <f t="shared" ca="1" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K12">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L12">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2435,32 +2983,19 @@
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="I13">
-        <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K13">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2468,32 +3003,19 @@
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="I14">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K14">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L14">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2501,50 +3023,25 @@
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="I15">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K15">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L15">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <f t="shared" ca="1" si="0"/>
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16">
         <v>0</v>
-      </c>
-      <c r="I16">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K16">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="L16">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -2552,31 +3049,18 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E17">
         <v>3</v>
       </c>
       <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="I17">
-        <f t="shared" ca="1" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K17">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L17">
-        <f t="shared" ca="1" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2585,32 +3069,19 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18">
-        <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
         <v>0</v>
-      </c>
-      <c r="I18">
-        <f t="shared" ca="1" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="K18">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="L18">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2618,32 +3089,19 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
         <v>0</v>
-      </c>
-      <c r="I19">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K19">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L19">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2651,32 +3109,19 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <f t="shared" ca="1" si="0"/>
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
         <v>0</v>
-      </c>
-      <c r="I20">
-        <f t="shared" ca="1" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="L20">
-        <f t="shared" ca="1" si="2"/>
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2684,32 +3129,19 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
         <v>0</v>
-      </c>
-      <c r="I21">
-        <f t="shared" ca="1" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K21">
-        <f t="shared" ca="1" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L21">
-        <f t="shared" ca="1" si="2"/>
-        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:24">
@@ -2849,4 +3281,286 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF01B7F4-A8F2-E74F-93E1-1ACB4B99B891}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>80</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4154E97-9715-C248-8300-688A466787B4}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="I6" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A04F2A-161E-4502-9547-1DD0A31CBA64}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="3" max="3" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0050A128-367E-6947-AFF1-621591FD31AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B1B40A-B982-7341-A617-C33996891041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -2074,15 +2074,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2140,15 +2140,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
       </c>
-      <c r="K4">
-        <f t="shared" ca="1" si="2"/>
-        <v>2</v>
-      </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -2173,11 +2173,11 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -2206,11 +2206,11 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2239,15 +2239,15 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2272,15 +2272,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <f t="shared" ca="1" si="2"/>
         <v>5</v>
-      </c>
-      <c r="L8">
-        <f t="shared" ca="1" si="2"/>
-        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -2305,15 +2305,15 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -2338,15 +2338,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2404,15 +2404,15 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2437,15 +2437,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -2470,15 +2470,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -2503,15 +2503,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -2536,11 +2536,11 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -2569,15 +2569,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2602,15 +2602,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2635,15 +2635,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2672,11 +2672,11 @@
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2701,15 +2701,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/HanSong_Model/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148DF50B-1AEA-FF44-B3C8-19FBE34AE74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FC812A-A378-AF48-A011-7AC332D2ED87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
   <si>
     <t>type</t>
   </si>
@@ -136,9 +136,6 @@
     <t>Base Vertiport</t>
   </si>
   <si>
-    <t>cap_flt</t>
-  </si>
-  <si>
     <t>cap_u</t>
   </si>
   <si>
@@ -172,18 +169,9 @@
     <t>e_{i,j} = 1%/km</t>
   </si>
   <si>
-    <t>rt_{i,j} = 0.6 min/km</t>
-  </si>
-  <si>
-    <t>capacity of air corridor</t>
-  </si>
-  <si>
     <t>seat capacity of eVTOL</t>
   </si>
   <si>
-    <t>5% battery charged per unit time</t>
-  </si>
-  <si>
     <t>minimum turnaround time at vertiport</t>
   </si>
   <si>
@@ -266,6 +254,36 @@
   </si>
   <si>
     <t>fd_sum</t>
+  </si>
+  <si>
+    <t>2,1% battery charged per unit time</t>
+  </si>
+  <si>
+    <t>rt_{i,j} = 0.2 min/km</t>
+  </si>
+  <si>
+    <t>unit time</t>
+  </si>
+  <si>
+    <t>b_penalty</t>
+  </si>
+  <si>
+    <t>penalty for not serving passengergroup</t>
+  </si>
+  <si>
+    <t>penalty for exceeding bmax</t>
+  </si>
+  <si>
+    <t>bmid</t>
+  </si>
+  <si>
+    <t>opening_cost</t>
+  </si>
+  <si>
+    <t>cost of opening a vertiport</t>
+  </si>
+  <si>
+    <t>minuts/unit</t>
   </si>
 </sst>
 </file>
@@ -273,8 +291,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -342,7 +360,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -353,7 +371,7 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -362,7 +380,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -707,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15C49E0-A7B4-734A-8962-DC2A879F4079}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="22.6640625" customWidth="1"/>
@@ -716,103 +734,104 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B2" s="5">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B3" s="5">
         <v>0.75</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B4" s="5">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5">
-        <v>1.51</v>
+        <v>300</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B6" s="5">
-        <v>0.3</v>
+        <v>1.51</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B7" s="5">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B8" s="5">
-        <v>1</v>
+        <f>0.2/B20</f>
+        <v>0.04</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="5">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -820,61 +839,98 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B11" s="5">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D11" s="4">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="B13" s="5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B14" s="5">
-        <v>20</v>
+        <f>2.11*B20</f>
+        <v>10.549999999999999</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5">
+        <f>30/B20</f>
+        <v>6</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5">
+        <f>20/B20</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="5">
         <v>120</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>47</v>
+      <c r="D17" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="5">
+        <v>5</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -907,7 +963,7 @@
         <v>20</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -922,7 +978,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -932,11 +988,11 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -955,7 +1011,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -965,7 +1021,7 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
@@ -973,7 +1029,7 @@
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -988,7 +1044,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1006,7 +1062,7 @@
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1021,7 +1077,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1031,15 +1087,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1054,7 +1110,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1064,15 +1120,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1087,7 +1143,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1097,7 +1153,7 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
@@ -1105,7 +1161,7 @@
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1120,7 +1176,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1134,11 +1190,11 @@
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1153,7 +1209,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1167,11 +1223,11 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1186,7 +1242,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1196,15 +1252,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1219,7 +1275,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1229,15 +1285,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1252,7 +1308,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1262,7 +1318,7 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
@@ -1285,7 +1341,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1295,15 +1351,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1318,7 +1374,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1328,11 +1384,11 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
@@ -1351,7 +1407,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1361,11 +1417,11 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
@@ -1384,7 +1440,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1398,11 +1454,11 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1417,7 +1473,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1427,15 +1483,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1450,7 +1506,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -1460,7 +1516,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
@@ -1468,7 +1524,7 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -1483,7 +1539,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1493,15 +1549,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -1516,7 +1572,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -1526,15 +1582,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -1549,7 +1605,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1559,11 +1615,11 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
@@ -1905,37 +1961,37 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="I1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="L1" s="8" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M1" s="9">
         <v>0.2</v>
@@ -1981,13 +2037,13 @@
         <v>4161</v>
       </c>
       <c r="L2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="M2" s="5">
         <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -2028,14 +2084,14 @@
         <v>1672</v>
       </c>
       <c r="L3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M3" s="5">
         <f>1000/60</f>
         <v>16.666666666666668</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2077,7 +2133,7 @@
         <v>2793</v>
       </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M4" s="5">
         <v>0.7</v>
@@ -2122,13 +2178,13 @@
         <v>2793</v>
       </c>
       <c r="L5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:14">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/asbb/Desktop/Speciale/Master-Thesis-eVTOL/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{148DF50B-1AEA-FF44-B3C8-19FBE34AE74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14DE58FB-AE23-164B-BD27-6A4DC7E32A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" activeTab="1" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -922,7 +922,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -932,15 +932,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -955,7 +955,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -965,15 +965,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -988,7 +988,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1031,15 +1031,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1130,15 +1130,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1163,11 +1163,11 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1229,15 +1229,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>88</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1266,11 +1266,11 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1328,11 +1328,11 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1361,15 +1361,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1427,15 +1427,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -1526,15 +1526,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1559,15 +1559,15 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:24">

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FC812A-A378-AF48-A011-7AC332D2ED87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8904C5-630C-4340-8F2B-69D62A7AD696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" firstSheet="1" activeTab="10" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="9" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="80">
   <si>
     <t>type</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>minuts/unit</t>
+  </si>
+  <si>
+    <t>time_old</t>
   </si>
 </sst>
 </file>
@@ -911,7 +914,8 @@
         <v>35</v>
       </c>
       <c r="B17" s="5">
-        <v>120</v>
+        <f>120/B20</f>
+        <v>24</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>43</v>
@@ -978,7 +982,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -996,7 +1000,7 @@
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1011,7 +1015,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1021,15 +1025,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1054,7 +1058,7 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1077,7 +1081,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1087,15 +1091,15 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1110,7 +1114,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1120,15 +1124,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1143,7 +1147,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1153,11 +1157,11 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -1176,7 +1180,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1186,7 +1190,7 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
@@ -1194,7 +1198,7 @@
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1209,7 +1213,7 @@
       </c>
       <c r="D9">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1219,11 +1223,11 @@
       </c>
       <c r="I9">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
@@ -1242,7 +1246,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1252,15 +1256,15 @@
       </c>
       <c r="I10">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1275,7 +1279,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1285,15 +1289,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1308,7 +1312,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1322,11 +1326,11 @@
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1341,7 +1345,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1355,11 +1359,11 @@
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1374,7 +1378,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1384,15 +1388,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1407,7 +1411,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1417,15 +1421,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1440,7 +1444,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1450,7 +1454,7 @@
       </c>
       <c r="I16">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
@@ -1458,7 +1462,7 @@
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1473,7 +1477,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1483,15 +1487,15 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L17">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:24">
@@ -1506,7 +1510,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -1516,15 +1520,15 @@
       </c>
       <c r="I18">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -1539,7 +1543,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1549,15 +1553,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -1572,7 +1576,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -1590,7 +1594,7 @@
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1615,11 +1619,11 @@
       </c>
       <c r="I21">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
@@ -1767,13 +1771,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3CF6DF-5DC6-4F82-AD2C-07BC625FD2D9}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1784,7 +1788,7 @@
         <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
         <v>19</v>
@@ -1792,8 +1796,11 @@
       <c r="F1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1812,8 +1819,12 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <f>D2/5</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1832,8 +1843,12 @@
       <c r="F3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <f t="shared" ref="G3:G8" si="0">D3/5</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1852,8 +1867,12 @@
       <c r="F4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1872,8 +1891,12 @@
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1892,8 +1915,12 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1912,8 +1939,12 @@
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1931,6 +1962,10 @@
       </c>
       <c r="F8">
         <v>1</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/HanSong_Model/inputData.xlsx
+++ b/HanSong_Model/inputData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/HanSong_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8904C5-630C-4340-8F2B-69D62A7AD696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA0515B-56FF-E646-A115-1A3CB6E9DFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" firstSheet="1" activeTab="10" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
@@ -982,7 +982,7 @@
       </c>
       <c r="D2">
         <f ca="1">RANDBETWEEN(10,120)</f>
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -992,15 +992,15 @@
       </c>
       <c r="I2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D21" ca="1" si="0">RANDBETWEEN(10,120)</f>
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -1025,15 +1025,15 @@
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I21" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <f t="shared" ref="K3:L21" ca="1" si="2">RANDBETWEEN(1,5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D4">
         <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1058,15 +1058,15 @@
       </c>
       <c r="I4">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D5">
         <f t="shared" ca="1" si="0"/>
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1091,11 +1091,11 @@
       </c>
       <c r="I5">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <f t="shared" ca="1" si="2"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="D6">
         <f t="shared" ca="1" si="0"/>
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1124,15 +1124,15 @@
       </c>
       <c r="I6">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D7">
         <f t="shared" ca="1" si="0"/>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1157,11 +1157,11 @@
       </c>
       <c r="I7">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7">
         <f t="shared" ca="1" si="2"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D8">
         <f t="shared" ca="1" si="0"/>
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1190,15 +1190,15 @@
       </c>
       <c r="I8">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="K9">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <f t="shared" ca="1" si="2"/>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D10">
         <f t="shared" ca="1" si="0"/>
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1260,11 +1260,11 @@
       </c>
       <c r="K10">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D11">
         <f t="shared" ca="1" si="0"/>
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1289,15 +1289,15 @@
       </c>
       <c r="I11">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="D12">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I12">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f t="shared" ca="1" si="2"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="L12">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D13">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1355,15 +1355,15 @@
       </c>
       <c r="I13">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K13">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D14">
         <f t="shared" ca="1" si="0"/>
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -1388,15 +1388,15 @@
       </c>
       <c r="I14">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D15">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -1421,15 +1421,15 @@
       </c>
       <c r="I15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D16">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:24">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="D17">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I17">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="2"/>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D18">
         <f t="shared" ca="1" si="0"/>
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:24">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="D19">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -1553,15 +1553,15 @@
       </c>
       <c r="I19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:24">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="D20">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -1586,15 +1586,15 @@
       </c>
       <c r="I20">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:24">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="D21">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -1623,11 +1623,11 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:24">
